--- a/Outputs/Scenarios/PtX_demand_PT_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PT_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004653717633502872</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002981202989058422</v>
+        <v>0.003243106961512187</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004968671648430703</v>
+        <v>0.004685965434744453</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>6.705219367598594e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001987468659372282</v>
+        <v>0.002008270900604766</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0006889262383035935</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01608682302358804</v>
+        <v>0.0175000789707683</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02681137170598007</v>
+        <v>0.02528586510883428</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>3.625927570018914e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01072454868239203</v>
+        <v>0.01083679933235755</v>
       </c>
     </row>
     <row r="43">
